--- a/artfynd/A 15850-2025 artfynd.xlsx
+++ b/artfynd/A 15850-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3120,6 +3120,909 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125543534</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98297</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>697161</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6364900</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125543543</v>
+      </c>
+      <c r="B24" t="n">
+        <v>109082</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>697093</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6364942</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125543554</v>
+      </c>
+      <c r="B25" t="n">
+        <v>109082</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>697002</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6364909</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125543567</v>
+      </c>
+      <c r="B26" t="n">
+        <v>109082</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>696924</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6364966</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet. Något tuvigt, troligen vinterfuktigt område.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125543528</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98297</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>697189</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6364882</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125543549</v>
+      </c>
+      <c r="B28" t="n">
+        <v>109082</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>697030</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6364977</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125543512</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98247</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>697146</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6364968</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125543515</v>
+      </c>
+      <c r="B30" t="n">
+        <v>109082</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>697152</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6364941</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15850-2025 artfynd.xlsx
+++ b/artfynd/A 15850-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3122,10 +3122,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125543534</v>
+        <v>125543543</v>
       </c>
       <c r="B23" t="n">
-        <v>98297</v>
+        <v>109082</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3134,20 +3134,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3155,31 +3155,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697161</v>
+        <v>697093</v>
       </c>
       <c r="R23" t="n">
-        <v>6364900</v>
+        <v>6364942</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3243,10 +3229,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125543543</v>
+        <v>125543534</v>
       </c>
       <c r="B24" t="n">
-        <v>109082</v>
+        <v>98297</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3255,20 +3241,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3276,17 +3262,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697093</v>
+        <v>697161</v>
       </c>
       <c r="R24" t="n">
-        <v>6364942</v>
+        <v>6364900</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125543554</v>
+        <v>125543528</v>
       </c>
       <c r="B25" t="n">
-        <v>109082</v>
+        <v>98297</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3362,20 +3362,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3383,17 +3383,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697002</v>
+        <v>697189</v>
       </c>
       <c r="R25" t="n">
-        <v>6364909</v>
+        <v>6364882</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3569,10 +3583,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125543528</v>
+        <v>125543515</v>
       </c>
       <c r="B27" t="n">
-        <v>98297</v>
+        <v>109082</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3581,20 +3595,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3602,31 +3616,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697189</v>
+        <v>697152</v>
       </c>
       <c r="R27" t="n">
-        <v>6364882</v>
+        <v>6364941</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3690,7 +3690,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125543549</v>
+        <v>125543554</v>
       </c>
       <c r="B28" t="n">
         <v>109082</v>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697030</v>
+        <v>697002</v>
       </c>
       <c r="R28" t="n">
-        <v>6364977</v>
+        <v>6364909</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125543512</v>
+        <v>125543549</v>
       </c>
       <c r="B29" t="n">
-        <v>98247</v>
+        <v>109082</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3809,52 +3809,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697146</v>
+        <v>697030</v>
       </c>
       <c r="R29" t="n">
-        <v>6364968</v>
+        <v>6364977</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3918,10 +3904,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125543515</v>
+        <v>125543512</v>
       </c>
       <c r="B30" t="n">
-        <v>109082</v>
+        <v>98247</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3930,38 +3916,52 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697152</v>
+        <v>697146</v>
       </c>
       <c r="R30" t="n">
-        <v>6364941</v>
+        <v>6364968</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4022,6 +4022,232 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125628684</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58345</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>697149</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6364892</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125628681</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>697153</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6364987</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Tall, död, med födosökshugg av spillkråka.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15850-2025 artfynd.xlsx
+++ b/artfynd/A 15850-2025 artfynd.xlsx
@@ -3122,15 +3122,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125543543</v>
+        <v>125543554</v>
       </c>
       <c r="B23" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3162,13 +3157,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697093</v>
+        <v>697002</v>
       </c>
       <c r="R23" t="n">
-        <v>6364942</v>
+        <v>6364909</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3232,12 +3227,7 @@
         <v>125543534</v>
       </c>
       <c r="B24" t="n">
-        <v>98297</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3350,32 +3340,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125543528</v>
+        <v>125543515</v>
       </c>
       <c r="B25" t="n">
-        <v>98297</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3383,31 +3368,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697189</v>
+        <v>697152</v>
       </c>
       <c r="R25" t="n">
-        <v>6364882</v>
+        <v>6364941</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3471,50 +3442,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125543567</v>
+        <v>125543512</v>
       </c>
       <c r="B26" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98302</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696924</v>
+        <v>697146</v>
       </c>
       <c r="R26" t="n">
-        <v>6364966</v>
+        <v>6364968</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3549,11 +3529,6 @@
           <t>2025-05-23</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3565,7 +3540,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet. Något tuvigt, troligen vinterfuktigt område.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3583,32 +3558,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125543515</v>
+        <v>125543528</v>
       </c>
       <c r="B27" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3616,17 +3586,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697152</v>
+        <v>697189</v>
       </c>
       <c r="R27" t="n">
-        <v>6364941</v>
+        <v>6364882</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3690,15 +3674,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125543554</v>
+        <v>125543567</v>
       </c>
       <c r="B28" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,10 +3709,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697002</v>
+        <v>696924</v>
       </c>
       <c r="R28" t="n">
-        <v>6364909</v>
+        <v>6364966</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3768,6 +3747,11 @@
           <t>2025-05-23</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3779,7 +3763,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkbarrskog med kontinuitet. Något tuvigt, troligen vinterfuktigt område.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3800,12 +3784,7 @@
         <v>125543549</v>
       </c>
       <c r="B29" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3904,67 +3883,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125543512</v>
+        <v>125543543</v>
       </c>
       <c r="B30" t="n">
-        <v>98247</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697146</v>
+        <v>697093</v>
       </c>
       <c r="R30" t="n">
-        <v>6364968</v>
+        <v>6364942</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4028,12 +3988,7 @@
         <v>125628684</v>
       </c>
       <c r="B31" t="n">
-        <v>58345</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58365</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4139,12 +4094,7 @@
         <v>125628681</v>
       </c>
       <c r="B32" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 15850-2025 artfynd.xlsx
+++ b/artfynd/A 15850-2025 artfynd.xlsx
@@ -3125,7 +3125,7 @@
         <v>125543554</v>
       </c>
       <c r="B23" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>125543534</v>
       </c>
       <c r="B24" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125543515</v>
       </c>
       <c r="B25" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>125543512</v>
       </c>
       <c r="B26" t="n">
-        <v>98302</v>
+        <v>98309</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>125543528</v>
       </c>
       <c r="B27" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>125543567</v>
       </c>
       <c r="B28" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>125543549</v>
       </c>
       <c r="B29" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>125543543</v>
       </c>
       <c r="B30" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 15850-2025 artfynd.xlsx
+++ b/artfynd/A 15850-2025 artfynd.xlsx
@@ -3125,7 +3125,7 @@
         <v>125543554</v>
       </c>
       <c r="B23" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>125543534</v>
       </c>
       <c r="B24" t="n">
-        <v>98359</v>
+        <v>98362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125543515</v>
       </c>
       <c r="B25" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>125543512</v>
       </c>
       <c r="B26" t="n">
-        <v>98309</v>
+        <v>98312</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>125543528</v>
       </c>
       <c r="B27" t="n">
-        <v>98359</v>
+        <v>98362</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>125543567</v>
       </c>
       <c r="B28" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>125543549</v>
       </c>
       <c r="B29" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>125543543</v>
       </c>
       <c r="B30" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>125628684</v>
       </c>
       <c r="B31" t="n">
-        <v>58365</v>
+        <v>58366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 15850-2025 artfynd.xlsx
+++ b/artfynd/A 15850-2025 artfynd.xlsx
@@ -3125,7 +3125,7 @@
         <v>125543554</v>
       </c>
       <c r="B23" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>125543534</v>
       </c>
       <c r="B24" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125543515</v>
       </c>
       <c r="B25" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>125543512</v>
       </c>
       <c r="B26" t="n">
-        <v>98312</v>
+        <v>98316</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>125543528</v>
       </c>
       <c r="B27" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>125543567</v>
       </c>
       <c r="B28" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>125543549</v>
       </c>
       <c r="B29" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>125543543</v>
       </c>
       <c r="B30" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 15850-2025 artfynd.xlsx
+++ b/artfynd/A 15850-2025 artfynd.xlsx
@@ -3125,7 +3125,7 @@
         <v>125543554</v>
       </c>
       <c r="B23" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>125543534</v>
       </c>
       <c r="B24" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125543515</v>
       </c>
       <c r="B25" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>125543512</v>
       </c>
       <c r="B26" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>125543528</v>
       </c>
       <c r="B27" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>125543567</v>
       </c>
       <c r="B28" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>125543549</v>
       </c>
       <c r="B29" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>125543543</v>
       </c>
       <c r="B30" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 15850-2025 artfynd.xlsx
+++ b/artfynd/A 15850-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3125,7 +3125,7 @@
         <v>125543554</v>
       </c>
       <c r="B23" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>125543534</v>
       </c>
       <c r="B24" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125543515</v>
       </c>
       <c r="B25" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>125543512</v>
       </c>
       <c r="B26" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>125543528</v>
       </c>
       <c r="B27" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>125543567</v>
       </c>
       <c r="B28" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>125543549</v>
       </c>
       <c r="B29" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>125543543</v>
       </c>
       <c r="B30" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>125628684</v>
       </c>
       <c r="B31" t="n">
-        <v>58366</v>
+        <v>58367</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>125628681</v>
       </c>
       <c r="B32" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4198,6 +4198,117 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126202334</v>
+      </c>
+      <c r="B33" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>696928</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6365068</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Flyger i skogen, på båda sidor om stigen</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Tallskog med inslag av löv, gran</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15850-2025 artfynd.xlsx
+++ b/artfynd/A 15850-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3125,7 +3125,7 @@
         <v>125543554</v>
       </c>
       <c r="B23" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>125543534</v>
       </c>
       <c r="B24" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3340,45 +3340,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125543515</v>
+        <v>125543512</v>
       </c>
       <c r="B25" t="n">
-        <v>109154</v>
+        <v>98321</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697152</v>
+        <v>697146</v>
       </c>
       <c r="R25" t="n">
-        <v>6364941</v>
+        <v>6364968</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3442,59 +3456,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125543512</v>
+        <v>125543515</v>
       </c>
       <c r="B26" t="n">
-        <v>98319</v>
+        <v>109156</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697146</v>
+        <v>697152</v>
       </c>
       <c r="R26" t="n">
-        <v>6364968</v>
+        <v>6364941</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3561,7 +3561,7 @@
         <v>125543528</v>
       </c>
       <c r="B27" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>125543567</v>
       </c>
       <c r="B28" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>125543549</v>
       </c>
       <c r="B29" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>125543543</v>
       </c>
       <c r="B30" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4310,6 +4310,324 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126243284</v>
+      </c>
+      <c r="B34" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>697024</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6364989</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126243286</v>
+      </c>
+      <c r="B35" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>696958</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6365064</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126243285</v>
+      </c>
+      <c r="B36" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>697017</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6364987</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15850-2025 artfynd.xlsx
+++ b/artfynd/A 15850-2025 artfynd.xlsx
@@ -3340,59 +3340,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125543512</v>
+        <v>125543515</v>
       </c>
       <c r="B25" t="n">
-        <v>98321</v>
+        <v>109156</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697146</v>
+        <v>697152</v>
       </c>
       <c r="R25" t="n">
-        <v>6364968</v>
+        <v>6364941</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3456,45 +3442,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125543515</v>
+        <v>125543512</v>
       </c>
       <c r="B26" t="n">
-        <v>109156</v>
+        <v>98321</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697152</v>
+        <v>697146</v>
       </c>
       <c r="R26" t="n">
-        <v>6364941</v>
+        <v>6364968</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>

--- a/artfynd/A 15850-2025 artfynd.xlsx
+++ b/artfynd/A 15850-2025 artfynd.xlsx
@@ -3988,7 +3988,7 @@
         <v>125628684</v>
       </c>
       <c r="B31" t="n">
-        <v>58367</v>
+        <v>58371</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>125628681</v>
       </c>
       <c r="B32" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 15850-2025 artfynd.xlsx
+++ b/artfynd/A 15850-2025 artfynd.xlsx
@@ -4204,7 +4204,7 @@
         <v>126202334</v>
       </c>
       <c r="B33" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>126243284</v>
       </c>
       <c r="B34" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>126243286</v>
       </c>
       <c r="B35" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>126243285</v>
       </c>
       <c r="B36" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 15850-2025 artfynd.xlsx
+++ b/artfynd/A 15850-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103791885</v>
+        <v>103791886</v>
       </c>
       <c r="B2" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hunninge, SV om Hejde, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697096.2154637387</v>
+        <v>697100</v>
       </c>
       <c r="R2" t="n">
-        <v>6364946.863326428</v>
+        <v>6365079</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +752,14 @@
           <t>2022-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-27</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 ex. i barrmatta under gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +768,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,43 +795,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104229903</v>
+        <v>112619245</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>3599</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697138.7277142562</v>
+        <v>697172</v>
       </c>
       <c r="R3" t="n">
-        <v>6364940.276824661</v>
+        <v>6365054</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,27 +869,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gamla gnagspår på nedfallen grov gren från levande tall.</t>
+          <t>1 ex. under gran och tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +888,17 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalktallskog.</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -932,48 +914,43 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+          <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112619259</v>
+        <v>112619258</v>
       </c>
       <c r="B4" t="n">
-        <v>85635</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696919</v>
+        <v>696929</v>
       </c>
       <c r="R4" t="n">
-        <v>6364999</v>
+        <v>6364986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca. 10 ex.</t>
+          <t>3 ex.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1057,65 +1034,51 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
+          <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112619260</v>
+        <v>120612463</v>
       </c>
       <c r="B5" t="n">
-        <v>85635</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hunninge, SV om Hejde, Gtl</t>
+          <t>Backhagen, Backhagen, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696942</v>
+        <v>697045</v>
       </c>
       <c r="R5" t="n">
-        <v>6365019</v>
+        <v>6365016</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1142,17 +1105,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca. 10 ex.</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,84 +1121,61 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112619256</v>
+        <v>120618376</v>
       </c>
       <c r="B6" t="n">
-        <v>85635</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hunninge, SV om Hejde, Gtl</t>
+          <t>Backhagen, Backhagen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697005</v>
+        <v>697193</v>
       </c>
       <c r="R6" t="n">
-        <v>6364958</v>
+        <v>6364976</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,17 +1202,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca. 20 ex.</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,40 +1218,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112619257</v>
+        <v>112619251</v>
       </c>
       <c r="B7" t="n">
-        <v>85635</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,26 +1245,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1362,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696989</v>
+        <v>697093</v>
       </c>
       <c r="R7" t="n">
-        <v>6364942</v>
+        <v>6365078</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1402,7 +1318,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 ex.</t>
+          <t>2 ex.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,21 +1348,16 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
+          <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112619262</v>
+        <v>120616943</v>
       </c>
       <c r="B8" t="n">
-        <v>85635</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,43 +1365,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hunninge, SV om Hejde, Gtl</t>
+          <t>Backhagen, Backhagen, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696960</v>
+        <v>697136</v>
       </c>
       <c r="R8" t="n">
-        <v>6365013</v>
+        <v>6365094</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1517,17 +1419,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca. 10 ex.</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,40 +1435,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112619253</v>
+        <v>112619265</v>
       </c>
       <c r="B9" t="n">
-        <v>85581</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87391</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,26 +1462,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>248955</v>
+        <v>3767</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1612,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697055</v>
+        <v>696979</v>
       </c>
       <c r="R9" t="n">
-        <v>6364977</v>
+        <v>6365078</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1652,7 +1535,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 ex. i barrmatta under gran.</t>
+          <t>4 ex. under gran, intill tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1660,11 +1543,6 @@
       </c>
       <c r="AE9" t="b">
         <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1687,21 +1565,16 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
+          <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112619258</v>
+        <v>125628681</v>
       </c>
       <c r="B10" t="n">
-        <v>85598</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,43 +1582,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3674</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hunninge, SV om Hejde, Gtl</t>
+          <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696929</v>
+        <v>697153</v>
       </c>
       <c r="R10" t="n">
-        <v>6364986</v>
+        <v>6364987</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1772,17 +1644,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>3 ex.</t>
+          <t>Tall, död, med födosökshugg av spillkråka.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1793,87 +1665,72 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112619263</v>
+        <v>125628682</v>
       </c>
       <c r="B11" t="n">
-        <v>85635</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hunninge, SV om Hejde, Gtl</t>
+          <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696985</v>
+        <v>697214</v>
       </c>
       <c r="R11" t="n">
-        <v>6365023</v>
+        <v>6364893</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1897,17 +1754,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2 ex.</t>
+          <t>Tall, död, med födosökshugg av spillkråka.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1918,40 +1775,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112619255</v>
+        <v>126202314</v>
       </c>
       <c r="B12" t="n">
-        <v>85635</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,46 +1802,54 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>101242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hunninge, SV om Hejde, Gtl</t>
+          <t>Klinte Hunninge 1:15, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697026</v>
+        <v>696929</v>
       </c>
       <c r="R12" t="n">
-        <v>6364979</v>
+        <v>6365078</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2022,17 +1873,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca. 5 ex.</t>
+          <t>Flyger i skogen, på båda sidor om stigen.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2041,83 +1892,76 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
+          <t>Tallskog med inslag av löv, gran</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
-        </is>
-      </c>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120610877</v>
+        <v>126202334</v>
       </c>
       <c r="B13" t="n">
-        <v>86271</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>248947</v>
+        <v>101242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Backhagen, Backhagen, Gtl</t>
+          <t>Klinte Hunninge 1:15, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>697035</v>
+        <v>696928</v>
       </c>
       <c r="R13" t="n">
-        <v>6364945</v>
+        <v>6365068</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2141,48 +1985,52 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Flyger i skogen, på båda sidor om stigen</t>
         </is>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Tallskog med inslag av löv, gran</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120611652</v>
+        <v>126243283</v>
       </c>
       <c r="B14" t="n">
-        <v>86255</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,37 +2038,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003295</v>
+        <v>101242</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Backhagen, Backhagen, Gtl</t>
+          <t>Klinte Hunninge 1:15, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697039</v>
+        <v>696963</v>
       </c>
       <c r="R14" t="n">
-        <v>6364963</v>
+        <v>6365089</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2244,12 +2101,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2264,27 +2121,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120610355</v>
+        <v>126243284</v>
       </c>
       <c r="B15" t="n">
-        <v>86255</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,37 +2144,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003295</v>
+        <v>101242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Backhagen, Backhagen, Gtl</t>
+          <t>Klinte Hunninge 1:15, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697006</v>
+        <v>697024</v>
       </c>
       <c r="R15" t="n">
-        <v>6364926</v>
+        <v>6364989</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2346,12 +2207,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2366,65 +2227,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120612144</v>
+        <v>126243285</v>
       </c>
       <c r="B16" t="n">
-        <v>86178</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>248956</v>
+        <v>101242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Backhagen, Backhagen, Gtl</t>
+          <t>Klinte Hunninge 1:15, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697012</v>
+        <v>697017</v>
       </c>
       <c r="R16" t="n">
-        <v>6364992</v>
+        <v>6364987</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2448,22 +2313,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:01</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:01</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2478,27 +2333,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120611367</v>
+        <v>126243286</v>
       </c>
       <c r="B17" t="n">
-        <v>86255</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,37 +2356,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>101242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Backhagen, Backhagen, Gtl</t>
+          <t>Klinte Hunninge 1:15, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697029</v>
+        <v>696958</v>
       </c>
       <c r="R17" t="n">
-        <v>6364944</v>
+        <v>6365064</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2560,12 +2419,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2580,65 +2439,69 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120613093</v>
+        <v>126243287</v>
       </c>
       <c r="B18" t="n">
-        <v>86178</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>248956</v>
+        <v>101242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Backhagen, Backhagen, Gtl</t>
+          <t>Klinte Hunninge 1:15, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697029</v>
+        <v>696962</v>
       </c>
       <c r="R18" t="n">
-        <v>6364993</v>
+        <v>6365092</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2662,22 +2525,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,27 +2545,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120613226</v>
+        <v>125628684</v>
       </c>
       <c r="B19" t="n">
-        <v>86255</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,37 +2568,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>103055</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Backhagen, Backhagen, Gtl</t>
+          <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697068</v>
+        <v>697149</v>
       </c>
       <c r="R19" t="n">
-        <v>6365018</v>
+        <v>6364892</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2774,12 +2631,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2794,27 +2651,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120612463</v>
+        <v>104229903</v>
       </c>
       <c r="B20" t="n">
-        <v>86219</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,34 +2674,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3674</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Backhagen, Backhagen, Gtl</t>
+          <t>Hunninge, SV om Hejde, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697045</v>
+        <v>697139</v>
       </c>
       <c r="R20" t="n">
-        <v>6365016</v>
+        <v>6364940</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2876,12 +2733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gamla gnagspår på nedfallen grov gren från levande tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,69 +2754,97 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120612462</v>
+        <v>125543512</v>
       </c>
       <c r="B21" t="n">
-        <v>86255</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6003295</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Backhagen, Backhagen, Gtl</t>
+          <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697012</v>
+        <v>697146</v>
       </c>
       <c r="R21" t="n">
-        <v>6364992</v>
+        <v>6364968</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2978,22 +2868,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,66 +2884,66 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120612408</v>
+        <v>94011444</v>
       </c>
       <c r="B22" t="n">
-        <v>86255</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6003295</v>
+        <v>219864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Backhagen, Backhagen, Gtl</t>
+          <t>Ygne-Hemse, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697045</v>
+        <v>697155</v>
       </c>
       <c r="R22" t="n">
-        <v>6365015</v>
+        <v>6364851</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,12 +2970,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,39 +2990,43 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125543554</v>
+        <v>125543520</v>
       </c>
       <c r="B23" t="n">
-        <v>109156</v>
+        <v>99147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3150,17 +3034,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697002</v>
+        <v>697211</v>
       </c>
       <c r="R23" t="n">
-        <v>6364909</v>
+        <v>6364921</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3224,10 +3122,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125543534</v>
+        <v>125543528</v>
       </c>
       <c r="B24" t="n">
-        <v>98371</v>
+        <v>99147</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3152,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3273,13 +3171,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697161</v>
+        <v>697189</v>
       </c>
       <c r="R24" t="n">
-        <v>6364900</v>
+        <v>6364882</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3340,27 +3238,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125543515</v>
+        <v>125543534</v>
       </c>
       <c r="B25" t="n">
-        <v>109156</v>
+        <v>99147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3368,20 +3266,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697152</v>
+        <v>697161</v>
       </c>
       <c r="R25" t="n">
-        <v>6364941</v>
+        <v>6364900</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3442,10 +3354,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125543512</v>
+        <v>125543557</v>
       </c>
       <c r="B26" t="n">
-        <v>98321</v>
+        <v>99147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,26 +3365,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>219864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3482,7 +3394,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3491,13 +3403,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697146</v>
+        <v>696944</v>
       </c>
       <c r="R26" t="n">
-        <v>6364968</v>
+        <v>6364874</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3540,7 +3452,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kraftledningsgata.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3558,62 +3470,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125543528</v>
+        <v>94011746</v>
       </c>
       <c r="B27" t="n">
-        <v>98371</v>
+        <v>108116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219864</v>
+        <v>220079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:15., Gtl</t>
+          <t>Ygne-Hemse, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697189</v>
+        <v>697120</v>
       </c>
       <c r="R27" t="n">
-        <v>6364882</v>
+        <v>6364856</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3637,12 +3535,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3653,31 +3551,30 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125543567</v>
+        <v>126202333</v>
       </c>
       <c r="B28" t="n">
-        <v>109156</v>
+        <v>108116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,34 +3582,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:15., Gtl</t>
+          <t>Klinte Hunninge 1:15, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696924</v>
+        <v>696866</v>
       </c>
       <c r="R28" t="n">
-        <v>6364966</v>
+        <v>6364950</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3739,17 +3636,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,28 +3655,28 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet. Något tuvigt, troligen vinterfuktigt område.</t>
+          <t>Tallskog med inslag av löv, gran</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125543549</v>
+        <v>125391462</v>
       </c>
       <c r="B29" t="n">
-        <v>109156</v>
+        <v>110078</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3816,10 +3708,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697030</v>
+        <v>696980</v>
       </c>
       <c r="R29" t="n">
-        <v>6364977</v>
+        <v>6365057</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3883,10 +3775,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125543543</v>
+        <v>125391464</v>
       </c>
       <c r="B30" t="n">
-        <v>109156</v>
+        <v>110078</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3918,13 +3810,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697093</v>
+        <v>696978</v>
       </c>
       <c r="R30" t="n">
-        <v>6364942</v>
+        <v>6365075</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3954,6 +3846,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3985,10 +3882,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125628684</v>
+        <v>125543515</v>
       </c>
       <c r="B31" t="n">
-        <v>58371</v>
+        <v>110078</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3996,46 +3893,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103055</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697149</v>
+        <v>697152</v>
       </c>
       <c r="R31" t="n">
-        <v>6364892</v>
+        <v>6364941</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4075,6 +3963,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4091,10 +3984,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125628681</v>
+        <v>125543543</v>
       </c>
       <c r="B32" t="n">
-        <v>57653</v>
+        <v>110078</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4102,42 +3995,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697153</v>
+        <v>697093</v>
       </c>
       <c r="R32" t="n">
-        <v>6364987</v>
+        <v>6364942</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4172,11 +4057,6 @@
           <t>2025-05-23</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Tall, död, med födosökshugg av spillkråka.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4185,6 +4065,11 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4201,10 +4086,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126202334</v>
+        <v>125543549</v>
       </c>
       <c r="B33" t="n">
-        <v>43228</v>
+        <v>110078</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4212,38 +4097,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:15, Gtl</t>
+          <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696928</v>
+        <v>697030</v>
       </c>
       <c r="R33" t="n">
-        <v>6365068</v>
+        <v>6364977</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4270,17 +4151,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Flyger i skogen, på båda sidor om stigen</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,28 +4170,28 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Tallskog med inslag av löv, gran</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126243284</v>
+        <v>125543554</v>
       </c>
       <c r="B34" t="n">
-        <v>43228</v>
+        <v>110078</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4323,43 +4199,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:15, Gtl</t>
+          <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697024</v>
+        <v>697002</v>
       </c>
       <c r="R34" t="n">
-        <v>6364989</v>
+        <v>6364909</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4386,12 +4253,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4402,26 +4269,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126243286</v>
+        <v>125543559</v>
       </c>
       <c r="B35" t="n">
-        <v>43228</v>
+        <v>110078</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,43 +4301,48 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:15, Gtl</t>
+          <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696958</v>
+        <v>696944</v>
       </c>
       <c r="R35" t="n">
-        <v>6365064</v>
+        <v>6364874</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4492,12 +4369,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4508,26 +4385,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126243285</v>
+        <v>125543567</v>
       </c>
       <c r="B36" t="n">
-        <v>43228</v>
+        <v>110078</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4535,43 +4417,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Klinte Hunninge 1:15, Gtl</t>
+          <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697017</v>
+        <v>696924</v>
       </c>
       <c r="R36" t="n">
-        <v>6364987</v>
+        <v>6364966</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4598,12 +4471,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4614,19 +4492,3102 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet. Något tuvigt, troligen vinterfuktigt område.</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126202316</v>
+      </c>
+      <c r="B37" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>696866</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6364933</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Tallskog med inslag av löv, gran</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
           <t>Gun Ingmansson</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>Gun Ingmansson</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126202318</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>696866</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6364933</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Tallskog med inslag av löv, gran</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>94011964</v>
+      </c>
+      <c r="B39" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>697160</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6364852</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2021-05-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2021-05-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>94011965</v>
+      </c>
+      <c r="B40" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>696923</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6364872</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2021-05-26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2021-05-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spridd</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120610877</v>
+      </c>
+      <c r="B41" t="n">
+        <v>87369</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Backhagen, Backhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>697035</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6364945</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>112619253</v>
+      </c>
+      <c r="B42" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hunninge, SV om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>697055</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6364978</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1 ex. i barrmatta under gran.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120612144</v>
+      </c>
+      <c r="B43" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Backhagen, Backhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>697012</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6364992</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120612829</v>
+      </c>
+      <c r="B44" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Backhagen, Backhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>697056</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6365025</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120613093</v>
+      </c>
+      <c r="B45" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Backhagen, Backhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>697029</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6364993</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>103791882</v>
+      </c>
+      <c r="B46" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hunninge, SV om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>697141</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6364849</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>103791885</v>
+      </c>
+      <c r="B47" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hunninge, SV om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>697097</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6364947</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>112619246</v>
+      </c>
+      <c r="B48" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hunninge, SV om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>697174</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6365061</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>3 ex.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>112619252</v>
+      </c>
+      <c r="B49" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hunninge, SV om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>697080</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6365035</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>3 ex.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>112619255</v>
+      </c>
+      <c r="B50" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hunninge, SV om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>697026</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6364979</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>112619256</v>
+      </c>
+      <c r="B51" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hunninge, SV om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>697005</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6364958</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ca. 20 ex.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>112619257</v>
+      </c>
+      <c r="B52" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hunninge, SV om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>696990</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6364942</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>1 ex.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>112619259</v>
+      </c>
+      <c r="B53" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hunninge, SV om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>696919</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6364999</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>112619260</v>
+      </c>
+      <c r="B54" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hunninge, SV om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>696942</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6365019</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>112619262</v>
+      </c>
+      <c r="B55" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hunninge, SV om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>696961</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6365014</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>112619263</v>
+      </c>
+      <c r="B56" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hunninge, SV om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>696986</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6365023</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>2 ex.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>112619264</v>
+      </c>
+      <c r="B57" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hunninge, SV om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>696985</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6365053</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>1 ex.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Äldre kalktallskog med inslag av gran och underskikt av enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120610355</v>
+      </c>
+      <c r="B58" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Backhagen, Backhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>697006</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6364926</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120611367</v>
+      </c>
+      <c r="B59" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Backhagen, Backhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>697029</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6364944</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120611652</v>
+      </c>
+      <c r="B60" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Backhagen, Backhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>697039</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6364963</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120612408</v>
+      </c>
+      <c r="B61" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Backhagen, Backhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>697045</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6365016</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120612462</v>
+      </c>
+      <c r="B62" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Backhagen, Backhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>697012</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6364992</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120613226</v>
+      </c>
+      <c r="B63" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Backhagen, Backhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>697068</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6365018</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>104229904</v>
+      </c>
+      <c r="B64" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hunninge, SV om Hejde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>697171</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6365088</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>4 ex.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15850-2025 artfynd.xlsx
+++ b/artfynd/A 15850-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY144"/>
+  <dimension ref="A1:AZ144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103791886</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,6 +927,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619245</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619258</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120612463</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120618376</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1351,6 +1381,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619251</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,6 +1483,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120616943</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619265</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1678,6 +1723,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125628681</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1788,6 +1838,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125628682</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1913,6 +1968,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126202314</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2024,6 +2084,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126202334</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2130,6 +2195,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243283</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2236,6 +2306,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243284</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2342,6 +2417,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243285</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2448,6 +2528,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243286</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2554,6 +2639,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243287</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2669,6 +2759,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621270</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2784,6 +2879,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621271</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2899,6 +2999,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621272</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3014,6 +3119,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621273</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3129,6 +3239,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621274</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3246,6 +3361,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621275</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3361,6 +3481,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621276</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3476,6 +3601,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621277</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3591,6 +3721,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621278</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3706,6 +3841,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621279</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3821,6 +3961,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621280</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3936,6 +4081,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621281</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4051,6 +4201,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621282</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4166,6 +4321,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621283</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4281,6 +4441,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621284</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4396,6 +4561,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621285</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4511,6 +4681,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621286</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4626,6 +4801,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621287</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4741,6 +4921,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621288</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4856,6 +5041,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621289</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4971,6 +5161,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621290</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5086,6 +5281,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621292</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5201,6 +5401,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621294</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5316,6 +5521,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621295</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5431,6 +5641,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621297</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5546,6 +5761,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621298</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5661,6 +5881,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621299</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5776,6 +6001,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621300</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5891,6 +6121,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621301</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6006,6 +6241,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621302</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6121,6 +6361,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621303</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6236,6 +6481,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621304</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6351,6 +6601,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621305</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6466,6 +6721,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621306</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6581,6 +6841,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621307</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6696,6 +6961,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621308</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6811,6 +7081,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621309</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6926,6 +7201,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621310</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7041,6 +7321,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621313</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7156,6 +7441,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621314</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7271,6 +7561,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621315</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7386,6 +7681,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621317</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7501,6 +7801,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621318</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7616,6 +7921,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621319</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7731,6 +8041,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621321</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7846,6 +8161,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621322</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7968,6 +8288,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621324</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8083,6 +8408,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621325</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8198,6 +8528,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621326</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8313,6 +8648,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621327</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8428,6 +8768,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621328</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8543,6 +8888,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621329</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8658,6 +9008,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621330</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8773,6 +9128,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621331</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8888,6 +9248,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621332</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9003,6 +9368,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621333</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9118,6 +9488,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621334</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9233,6 +9608,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621335</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9348,6 +9728,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621337</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9463,6 +9848,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621339</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9578,6 +9968,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621340</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9693,6 +10088,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621342</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9808,6 +10208,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621344</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9915,6 +10320,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624832</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10022,6 +10432,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624833</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10129,6 +10544,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624834</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10236,6 +10656,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624835</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10348,6 +10773,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624837</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10455,6 +10885,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624838</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10562,6 +10997,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624840</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10674,6 +11114,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624841</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10781,6 +11226,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624842</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10888,6 +11338,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624844</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11006,6 +11461,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624845</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11113,6 +11573,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624847</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11225,6 +11690,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624849</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11337,6 +11807,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624850</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11454,6 +11929,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629322</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11560,6 +12040,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125628684</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11686,6 +12171,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104229903</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11802,6 +12292,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125543512</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11909,6 +12404,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621291</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12016,6 +12516,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621312</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12117,6 +12622,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011444</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12233,6 +12743,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125543520</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12349,6 +12864,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125543528</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12465,6 +12985,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125543534</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12581,6 +13106,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125543557</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12682,6 +13212,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011746</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12784,6 +13319,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126202333</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12886,6 +13426,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125391462</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12993,6 +13538,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125391464</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13095,6 +13645,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125543515</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13197,6 +13752,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125543543</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13299,6 +13859,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125543549</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13401,6 +13966,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125543554</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13517,6 +14087,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125543559</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13624,6 +14199,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125543567</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13726,6 +14306,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126202316</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13832,6 +14417,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126202318</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13933,6 +14523,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011964</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14037,6 +14632,11 @@
       <c r="AY120" t="inlineStr">
         <is>
           <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011965</t>
         </is>
       </c>
     </row>
@@ -14140,6 +14740,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120610877</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14265,6 +14870,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619253</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14372,6 +14982,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120612144</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14469,6 +15084,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120612829</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14576,6 +15196,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120613093</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14683,6 +15308,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103791882</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14790,6 +15420,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103791885</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14910,6 +15545,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619246</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15030,6 +15670,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619252</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15150,6 +15795,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619255</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15270,6 +15920,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619256</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15390,6 +16045,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619257</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15510,6 +16170,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619259</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15630,6 +16295,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619260</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15750,6 +16420,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619262</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15870,6 +16545,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619263</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15990,6 +16670,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619264</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16087,6 +16772,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120610355</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16184,6 +16874,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120611367</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16281,6 +16976,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120611652</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16378,6 +17078,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120612408</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16485,6 +17190,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120612462</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16582,6 +17292,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120613226</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16702,8 +17417,158 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104229904</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>